--- a/static/data/exports/Retro_GA_GE_2009.xlsx
+++ b/static/data/exports/Retro_GA_GE_2009.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="Q2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>6</v>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="Q10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>6</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="Q16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>6</v>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="Q24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>6</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="Q30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>6</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="Q37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>6</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Q44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>6</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="Q52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
         <v>6</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="Q58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
         <v>6</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="Q66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
         <v>6</v>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="Q72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
         <v>6</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Q80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" t="n">
         <v>6</v>
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="Q87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" t="n">
         <v>6</v>
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="Q94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
         <v>6</v>
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="Q101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" t="n">
         <v>6</v>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="Q107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" t="n">
         <v>6</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Q114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" t="n">
         <v>6</v>
@@ -8017,7 +8017,7 @@
         </is>
       </c>
       <c r="Q122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" t="n">
         <v>6</v>
@@ -8451,7 +8451,7 @@
         </is>
       </c>
       <c r="Q129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R129" t="n">
         <v>6</v>
@@ -8823,7 +8823,7 @@
         </is>
       </c>
       <c r="Q135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R135" t="n">
         <v>6</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Q143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R143" t="n">
         <v>6</v>
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="Q153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R153" t="n">
         <v>6</v>
@@ -10683,7 +10683,7 @@
         </is>
       </c>
       <c r="Q165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R165" t="n">
         <v>6</v>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="Q176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R176" t="n">
         <v>6</v>
@@ -12047,7 +12047,7 @@
         </is>
       </c>
       <c r="Q187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R187" t="n">
         <v>6</v>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="Q197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R197" t="n">
         <v>6</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="Q208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R208" t="n">
         <v>6</v>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="Q219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R219" t="n">
         <v>6</v>
@@ -14713,7 +14713,7 @@
         </is>
       </c>
       <c r="Q230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R230" t="n">
         <v>6</v>
@@ -15395,7 +15395,7 @@
         </is>
       </c>
       <c r="Q241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R241" t="n">
         <v>6</v>
@@ -15845,11 +15845,11 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1494449</v>
+        <v>1494450</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Dias Jawahar</t>
+          <t>Mulla Salim</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15882,7 +15882,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Dias Jawahar</t>
+          <t>Mulla Salim</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -15907,11 +15907,11 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1494450</v>
+        <v>1494449</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Mulla Salim</t>
+          <t>Dias Jawahar</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15944,7 +15944,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Mulla Salim</t>
+          <t>Dias Jawahar</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -16077,7 +16077,7 @@
         </is>
       </c>
       <c r="Q252" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R252" t="n">
         <v>6</v>
@@ -16759,7 +16759,7 @@
         </is>
       </c>
       <c r="Q263" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R263" t="n">
         <v>6</v>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="Q274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R274" t="n">
         <v>6</v>
@@ -18123,7 +18123,7 @@
         </is>
       </c>
       <c r="Q285" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R285" t="n">
         <v>6</v>
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="Q296" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R296" t="n">
         <v>6</v>
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="Q307" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R307" t="n">
         <v>6</v>
@@ -20231,7 +20231,7 @@
         </is>
       </c>
       <c r="Q319" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R319" t="n">
         <v>6</v>
@@ -20913,7 +20913,7 @@
         </is>
       </c>
       <c r="Q330" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R330" t="n">
         <v>6</v>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="Q341" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R341" t="n">
         <v>6</v>
@@ -22277,7 +22277,7 @@
         </is>
       </c>
       <c r="Q352" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R352" t="n">
         <v>6</v>
